--- a/Planification/Planification_G2.xlsx
+++ b/Planification/Planification_G2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brando.colamarco\Documents\GitHub\mini-projet2\Planification\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfelixlasalle-my.sharepoint.com/personal/yoann_gnangla_stfelixlasalle_fr/Documents/Mini_projet_2_grp2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8BF8F93-FFDE-4D4B-9903-24EF02954AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="11_9248CACD84F5E813E97046798E3E8C1851038385" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBBA9FB5-1EA3-4C51-AEB6-4AC559150C05}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>Tache</t>
   </si>
@@ -86,7 +86,34 @@
     <t>Vento absent 20/03/2026</t>
   </si>
   <si>
-    <t>Relier le code python et l'HTML</t>
+    <t>Continuer interfaces HTML/CSS</t>
+  </si>
+  <si>
+    <t>Yoann, Brando</t>
+  </si>
+  <si>
+    <t>Continuer interfaces HTML/CSS et les relier</t>
+  </si>
+  <si>
+    <t>Vento</t>
+  </si>
+  <si>
+    <t>2h30</t>
+  </si>
+  <si>
+    <t>backend (serveur pour se connecter et créer un pseudo)</t>
+  </si>
+  <si>
+    <t>Mettre a jour nos fichiers Journal d'activités</t>
+  </si>
+  <si>
+    <t>Brando, Yoann, Vento</t>
+  </si>
+  <si>
+    <t>5min</t>
+  </si>
+  <si>
+    <t>Planifier ce que l'on va faire</t>
   </si>
 </sst>
 </file>
@@ -155,7 +182,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -451,10 +478,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.7109375" customWidth="1"/>
+    <col min="1" max="1" width="51.7109375" customWidth="1"/>
     <col min="2" max="2" width="47.140625" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
     <col min="4" max="4" width="16.42578125" customWidth="1"/>
@@ -521,7 +548,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -531,22 +558,79 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B9" t="s">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="1">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>15</v>
+      <c r="D11" s="1">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="1">
+        <v>46108</v>
       </c>
     </row>
   </sheetData>

--- a/Planification/Planification_G2.xlsx
+++ b/Planification/Planification_G2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfelixlasalle-my.sharepoint.com/personal/yoann_gnangla_stfelixlasalle_fr/Documents/Mini_projet_2_grp2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="11_9248CACD84F5E813E97046798E3E8C1851038385" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBBA9FB5-1EA3-4C51-AEB6-4AC559150C05}"/>
+  <xr:revisionPtr revIDLastSave="129" documentId="11_9248CACD84F5E813E97046798E3E8C1851038385" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4598FCA9-23EA-47A2-90AB-97155BE116AB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>Tache</t>
   </si>
@@ -86,21 +86,12 @@
     <t>Vento absent 20/03/2026</t>
   </si>
   <si>
-    <t>Continuer interfaces HTML/CSS</t>
-  </si>
-  <si>
     <t>Yoann, Brando</t>
   </si>
   <si>
-    <t>Continuer interfaces HTML/CSS et les relier</t>
-  </si>
-  <si>
     <t>Vento</t>
   </si>
   <si>
-    <t>2h30</t>
-  </si>
-  <si>
     <t>backend (serveur pour se connecter et créer un pseudo)</t>
   </si>
   <si>
@@ -114,6 +105,36 @@
   </si>
   <si>
     <t>Planifier ce que l'on va faire</t>
+  </si>
+  <si>
+    <t>Continuer l'interface de Connexion</t>
+  </si>
+  <si>
+    <t>Commencer l'interface de conversation d'utilisateurs</t>
+  </si>
+  <si>
+    <t>Commencer l'interface de conversation de groupe</t>
+  </si>
+  <si>
+    <t>Relier l'interface d'inscription et l'interface de connexion</t>
+  </si>
+  <si>
+    <t>15min</t>
+  </si>
+  <si>
+    <t>Relier l'interface de connexion à celle de la conversation</t>
+  </si>
+  <si>
+    <t>Coder l'envoi des messages dans la conversation</t>
+  </si>
+  <si>
+    <t>1h00</t>
+  </si>
+  <si>
+    <t>3h00</t>
+  </si>
+  <si>
+    <t>3h30</t>
   </si>
 </sst>
 </file>
@@ -478,10 +499,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.7109375" customWidth="1"/>
+    <col min="1" max="1" width="62.140625" customWidth="1"/>
     <col min="2" max="2" width="47.140625" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
     <col min="4" max="4" width="16.42578125" customWidth="1"/>
@@ -548,7 +569,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -565,10 +586,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
@@ -579,13 +600,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1">
         <v>46108</v>
@@ -593,13 +614,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1">
         <v>46108</v>
@@ -607,10 +628,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -621,15 +642,71 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="1">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="1">
         <v>46108</v>
       </c>
     </row>

--- a/Planification/Planification_G2.xlsx
+++ b/Planification/Planification_G2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfelixlasalle-my.sharepoint.com/personal/yoann_gnangla_stfelixlasalle_fr/Documents/Mini_projet_2_grp2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brando.colamarco\Documents\GitHub\mini-projet2\Planification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="11_9248CACD84F5E813E97046798E3E8C1851038385" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4598FCA9-23EA-47A2-90AB-97155BE116AB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BA9027-1832-4E11-AF2D-EDBFBE546CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
   <si>
     <t>Tache</t>
   </si>
@@ -135,6 +135,12 @@
   </si>
   <si>
     <t>3h30</t>
+  </si>
+  <si>
+    <t>Ajouter la fonctionnalité d'ajouter des contacts</t>
+  </si>
+  <si>
+    <t>Ajouter la fonctionnalité de pouvoir discuter avec un autre utilisateur</t>
   </si>
 </sst>
 </file>
@@ -196,10 +202,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -499,10 +501,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="62.140625" customWidth="1"/>
+    <col min="1" max="1" width="64.28515625" customWidth="1"/>
     <col min="2" max="2" width="47.140625" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
     <col min="4" max="4" width="16.42578125" customWidth="1"/>
@@ -710,6 +712,65 @@
         <v>46108</v>
       </c>
     </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="1">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="1">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="1">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="1">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D23" s="1">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D24" s="1">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/Planification/Planification_G2.xlsx
+++ b/Planification/Planification_G2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brando.colamarco\Documents\GitHub\mini-projet2\Planification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BA9027-1832-4E11-AF2D-EDBFBE546CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845109E6-0021-4D09-8381-EB79FD8F1498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="39">
   <si>
     <t>Tache</t>
   </si>
@@ -141,6 +141,18 @@
   </si>
   <si>
     <t>Ajouter la fonctionnalité de pouvoir discuter avec un autre utilisateur</t>
+  </si>
+  <si>
+    <t>Continuer interface de conversation</t>
+  </si>
+  <si>
+    <t>Lier l'IHM de conversation avec le serveur</t>
+  </si>
+  <si>
+    <t>3h</t>
+  </si>
+  <si>
+    <t>Tester et vérifier le fonctionnement de notre chat multi-utilisateurs</t>
   </si>
 </sst>
 </file>
@@ -501,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="64.28515625" customWidth="1"/>
@@ -719,6 +731,9 @@
       <c r="B19" t="s">
         <v>20</v>
       </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
       <c r="D19" s="1">
         <v>46111</v>
       </c>
@@ -730,6 +745,9 @@
       <c r="B20" t="s">
         <v>17</v>
       </c>
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
       <c r="D20" s="1">
         <v>46111</v>
       </c>
@@ -741,34 +759,67 @@
       <c r="B21" t="s">
         <v>17</v>
       </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
       <c r="D21" s="1">
         <v>46111</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
       <c r="D22" s="1">
         <v>46111</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>37</v>
+      </c>
       <c r="D23" s="1">
         <v>46111</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
       <c r="D24" s="1">
         <v>46111</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>19</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B25" t="s">
         <v>20</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C25" t="s">
         <v>21</v>
+      </c>
+      <c r="D25" s="1">
+        <v>46111</v>
       </c>
     </row>
   </sheetData>

--- a/Planification/Planification_G2.xlsx
+++ b/Planification/Planification_G2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brando.colamarco\Documents\GitHub\mini-projet2\Planification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845109E6-0021-4D09-8381-EB79FD8F1498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3210ED85-B116-4CC7-897B-A272BDD40F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="40">
   <si>
     <t>Tache</t>
   </si>
@@ -153,6 +154,9 @@
   </si>
   <si>
     <t>Tester et vérifier le fonctionnement de notre chat multi-utilisateurs</t>
+  </si>
+  <si>
+    <t>Yoann, Vento</t>
   </si>
 </sst>
 </file>
@@ -799,7 +803,7 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
